--- a/backend/src/main/resources/templates/excels/import_question.xlsx
+++ b/backend/src/main/resources/templates/excels/import_question.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C122C63-0E38-4234-93DA-C02C385E3ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421C132D-965D-483E-80AA-AEEA77FDF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{D9B75CC3-C212-473C-B437-A7386A8908BA}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="4" xr2:uid="{D9B75CC3-C212-473C-B437-A7386A8908BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Trắc nghiệm đúng sai" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="129">
   <si>
     <t>STT</t>
   </si>
@@ -64,45 +64,24 @@
     <t>Correct Answer Index</t>
   </si>
   <si>
-    <t>Java là ngôn ngữ gì?</t>
-  </si>
-  <si>
     <t>java,programming</t>
   </si>
   <si>
-    <t>Ngôn ngữ lập trình hướng đối tượng | Ngôn ngữ thủ tục | Ngôn ngữ script | Ngôn ngữ markup</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
     <t>NORMAL</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>ABADFASDFASDF</t>
-  </si>
-  <si>
-    <t>Hello ????</t>
-  </si>
-  <si>
     <t>Expected Answer</t>
   </si>
   <si>
-    <t>fasdfasdfasf1</t>
-  </si>
-  <si>
     <t>Extract Match</t>
   </si>
   <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>Câu hỏi plain text</t>
-  </si>
-  <si>
     <t>Max Words</t>
   </si>
   <si>
@@ -112,20 +91,347 @@
     <t>Simple Answers</t>
   </si>
   <si>
-    <t>FALSEfasdfasdf</t>
-  </si>
-  <si>
     <t>Grading Criteria</t>
   </si>
   <si>
     <t>Không có</t>
+  </si>
+  <si>
+    <t>Java là ngôn ngữ lập trình loại nào?</t>
+  </si>
+  <si>
+    <t>Scripting | Biên dịch (Compiled) &amp; Thông dịch (Interpreted) | Chỉ biên dịch | Low-level</t>
+  </si>
+  <si>
+    <t>Port mặc định của Tomcat trong Spring Boot là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>EASY</t>
+  </si>
+  <si>
+    <t>80 | 3306 | 8080 | 5432</t>
+  </si>
+  <si>
+    <t>Annotation nào dùng để đánh dấu một Class là Entity trong JPA?</t>
+  </si>
+  <si>
+    <t>DIFFICULT</t>
+  </si>
+  <si>
+    <t>@Table | @Entity | @Id | @Object</t>
+  </si>
+  <si>
+    <t>Trong CSS, thuộc tính nào dùng để đổi màu chữ?</t>
+  </si>
+  <si>
+    <t>background-color | text-style | color | font-color</t>
+  </si>
+  <si>
+    <t>Thẻ HTML nào là lớn nhất trong các thẻ tiêu đề?</t>
+  </si>
+  <si>
+    <t>h6 | h1 | header | title</t>
+  </si>
+  <si>
+    <t>HTTP Status Code 404 nghĩa là gì?</t>
+  </si>
+  <si>
+    <t>Server Error | Unauthorized | Not Found  | Success</t>
+  </si>
+  <si>
+    <t>List trong Java thuộc package nào?</t>
+  </si>
+  <si>
+    <t>java.io | java.lang | java.util | java.sql</t>
+  </si>
+  <si>
+    <t>Để khai báo biến hằng số trong Java, ta dùng từ khóa nào?</t>
+  </si>
+  <si>
+    <t>const | final | static | immutable</t>
+  </si>
+  <si>
+    <t>Frontend Framework nào được phát triển bởi Facebook (Meta)?</t>
+  </si>
+  <si>
+    <t>Vue.js | Angular | React | Svelte</t>
+  </si>
+  <si>
+    <t>Hàm main trong Java có kiểu trả về là gì?</t>
+  </si>
+  <si>
+    <t>int | String | void | boolean</t>
+  </si>
+  <si>
+    <t>Trong mô hình MVC, chữ "V" viết tắt của?</t>
+  </si>
+  <si>
+    <t>Verification | View | Variable | Virtual</t>
+  </si>
+  <si>
+    <t>SQL là viết tắt của?</t>
+  </si>
+  <si>
+    <t>Structured Query Language | Strong Question Language | Structured Quick Language | System Query Logic</t>
+  </si>
+  <si>
+    <t>Những đặc điểm chính của OOP là gì? (Chọn 3)</t>
+  </si>
+  <si>
+    <t>Đóng gói (Encapsulation) | Kế thừa (Inheritance)  | Đa hình (Polymorphism)  | Đệ quy (Recursion)</t>
+  </si>
+  <si>
+    <t>0, 1, 2</t>
+  </si>
+  <si>
+    <t>Các phương thức HTTP nào thường dùng trong RESTful API? (Chọn 3)</t>
+  </si>
+  <si>
+    <t>GET  | POST | DELETE  | STOP</t>
+  </si>
+  <si>
+    <t>Những thẻ nào là thẻ Block trong HTML? (Chọn 2)</t>
+  </si>
+  <si>
+    <t>&lt;div&gt; | &lt;span&gt; | &lt;p&gt;  | &lt;a&gt;</t>
+  </si>
+  <si>
+    <t>0, 2</t>
+  </si>
+  <si>
+    <t>Các hệ quản trị CSDL quan hệ (RDBMS) phổ biến? (Chọn 2)</t>
+  </si>
+  <si>
+    <t>MySQL | MongoDB | PostgreSQL | Redis</t>
+  </si>
+  <si>
+    <t>Trong file application.properties của Spring Boot, cấu hình nào liên quan đến Database? (Chọn 2)</t>
+  </si>
+  <si>
+    <t>spring.datasource.url | server.port | spring.datasource.username  | spring.application.name</t>
+  </si>
+  <si>
+    <t>Các scope của Spring Bean gồm những gì? (Chọn 2)</t>
+  </si>
+  <si>
+    <t>Singleton | Prototype  | Public | Private</t>
+  </si>
+  <si>
+    <t>0, 1</t>
+  </si>
+  <si>
+    <t>Các kiểu dữ liệu nguyên thủy (Primitive) trong Java? (Chọn 3)</t>
+  </si>
+  <si>
+    <t>0, 2, 3</t>
+  </si>
+  <si>
+    <t>Interface Collection trong Java là cha của những Interface nào? (Chọn 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int | String | double | boolean </t>
+  </si>
+  <si>
+    <t>List | Set  | Map | Arrays</t>
+  </si>
+  <si>
+    <t>Để định dạng Layout trong CSS, ta có thể dùng? (Chọn 2)</t>
+  </si>
+  <si>
+    <t>Flexbox  | Grid  | Color | Font-size</t>
+  </si>
+  <si>
+    <t>Java hỗ trợ đa kế thừa (Multiple Inheritance) thông qua Class.</t>
+  </si>
+  <si>
+    <t>String trong Java là kiểu dữ liệu bất biến (Immutable).</t>
+  </si>
+  <si>
+    <t>HTML là một ngôn ngữ lập trình.</t>
+  </si>
+  <si>
+    <t>Spring Boot yêu cầu phải cấu hình file XML để chạy.</t>
+  </si>
+  <si>
+    <t>ArrayList truy xuất phần tử nhanh hơn LinkedList.</t>
+  </si>
+  <si>
+    <t>Constructor có thể có kiểu trả về.</t>
+  </si>
+  <si>
+    <t>JSON là viết tắt của JavaScript Object Notation.</t>
+  </si>
+  <si>
+    <t>Primary Key trong Database có thể nhận giá trị NULL.</t>
+  </si>
+  <si>
+    <t>Từ khóa nào dùng để tạo đối tượng mới trong Java?</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>1 byte bằng bao nhiêu bit?</t>
+  </si>
+  <si>
+    <t>Cấu trúc dữ liệu nào hoạt động theo nguyên tắc LIFO (Last In First Out)?</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Để kế thừa một class trong Java, ta dùng từ khóa gì?</t>
+  </si>
+  <si>
+    <t>extends</t>
+  </si>
+  <si>
+    <t>Tên file cấu hình quản lý dependency trong dự án Maven là gì?</t>
+  </si>
+  <si>
+    <t>pom.xml</t>
+  </si>
+  <si>
+    <t>Trình bày sự khác nhau giữa Interface và Abstract Class trong Java.</t>
+  </si>
+  <si>
+    <t>Giải thích khái niệm Dependency Injection (DI) trong Spring Framework.</t>
+  </si>
+  <si>
+    <t>Phân tích ưu nhược điểm của việc sử dụng Microservices so với Monolithic.</t>
+  </si>
+  <si>
+    <t>Mô tả vòng đời (Life Cycle) của một React Component</t>
+  </si>
+  <si>
+    <t>Viết một đoạn văn ngắn giới thiệu về bản thân và kinh nghiệm lập trình.</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_001</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_002</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_003</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_004</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_005</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_006</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_007</t>
+  </si>
+  <si>
+    <t>QUES_TRUE_FALSE_008</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_001</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_002</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_003</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_004</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_005</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_006</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_007</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_008</t>
+  </si>
+  <si>
+    <t>QUES_MUL_CHOICE_009</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_001</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_002</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_003</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_004</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_005</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_006</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_007</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_008</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_009</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_010</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_011</t>
+  </si>
+  <si>
+    <t>QUES_ONE_CHOICE_012</t>
+  </si>
+  <si>
+    <t>QUES_PLAIN_001</t>
+  </si>
+  <si>
+    <t>QUES_PLAIN_002</t>
+  </si>
+  <si>
+    <t>QUES_PLAIN_003</t>
+  </si>
+  <si>
+    <t>QUES_PLAIN_004</t>
+  </si>
+  <si>
+    <t>QUES_PLAIN_005</t>
+  </si>
+  <si>
+    <t>QUES_ESSAY_001</t>
+  </si>
+  <si>
+    <t>QUES_ESSAY_002</t>
+  </si>
+  <si>
+    <t>QUES_ESSAY_003</t>
+  </si>
+  <si>
+    <t>QUES_ESSAY_004</t>
+  </si>
+  <si>
+    <t>QUES_ESSAY_005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +443,18 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -162,9 +480,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,11 +799,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAE31E5-414E-4811-ABA0-10FD9748A6EB}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -512,29 +832,170 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -542,11 +1003,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A718FCF-BEED-44F7-93A9-6FC18032802F}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="83.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -579,32 +1040,217 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -612,11 +1258,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055D0DFC-56EF-45B5-A3A9-EDC98D0D031F}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="83.21875" bestFit="1" customWidth="1"/>
@@ -650,18 +1296,18 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>107</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -669,13 +1315,267 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -683,11 +1583,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BEEA59-D650-40A7-9A86-A2A07F6A257F}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -714,27 +1614,27 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -743,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -752,7 +1652,112 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -760,11 +1765,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DF16D5-F6DD-450A-967F-374511ACFF6B}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -792,51 +1797,168 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>500</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1000</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>120</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
